--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N84_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N84_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.32569109174752</v>
+        <v>12.07792480240897</v>
       </c>
       <c r="D2" t="n">
-        <v>74.11871686402567</v>
+        <v>12.04429149040417</v>
       </c>
       <c r="E2" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F2" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>93.73506405371104</v>
+        <v>15.23194790872805</v>
       </c>
       <c r="D3" t="n">
-        <v>93.62076545248972</v>
+        <v>15.21337438602958</v>
       </c>
       <c r="E3" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F3" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>77.83401347103919</v>
+        <v>12.64802718904387</v>
       </c>
       <c r="D4" t="n">
-        <v>77.68228382678805</v>
+        <v>12.62337112185306</v>
       </c>
       <c r="E4" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F4" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.66531099972593</v>
+        <v>7.095613037455463</v>
       </c>
       <c r="D5" t="n">
-        <v>43.29710593412801</v>
+        <v>7.035779714295801</v>
       </c>
       <c r="E5" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F5" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>66.89046766709187</v>
+        <v>10.86970099590243</v>
       </c>
       <c r="D6" t="n">
-        <v>66.61980162069814</v>
+        <v>10.82571776336345</v>
       </c>
       <c r="E6" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F6" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.23196434596667</v>
+        <v>6.862694206219584</v>
       </c>
       <c r="D7" t="n">
-        <v>41.90725377378694</v>
+        <v>6.809928738240378</v>
       </c>
       <c r="E7" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F7" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.10742748091791</v>
+        <v>9.11745696564916</v>
       </c>
       <c r="D8" t="n">
-        <v>55.83616633681211</v>
+        <v>9.073377029731969</v>
       </c>
       <c r="E8" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F8" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>76.79215949598908</v>
+        <v>12.47872591809823</v>
       </c>
       <c r="D9" t="n">
-        <v>76.73644212768853</v>
+        <v>12.46967184574939</v>
       </c>
       <c r="E9" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F9" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.46349823034158</v>
+        <v>7.550318462430507</v>
       </c>
       <c r="D10" t="n">
-        <v>46.3466973153553</v>
+        <v>7.531338313745237</v>
       </c>
       <c r="E10" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F10" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.88693432091549</v>
+        <v>5.506626827148767</v>
       </c>
       <c r="D11" t="n">
-        <v>33.68495639260888</v>
+        <v>5.473805413798943</v>
       </c>
       <c r="E11" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F11" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.45142066652524</v>
+        <v>2.510855858310351</v>
       </c>
       <c r="D12" t="n">
-        <v>15.29071182255812</v>
+        <v>2.484740671165694</v>
       </c>
       <c r="E12" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F12" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41242837458708</v>
+        <v>3.8045196108704</v>
       </c>
       <c r="D13" t="n">
-        <v>23.26749227724209</v>
+        <v>3.780967495051839</v>
       </c>
       <c r="E13" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F13" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>56.07786462033511</v>
+        <v>9.112653000804455</v>
       </c>
       <c r="D14" t="n">
-        <v>55.9477466880737</v>
+        <v>9.091508836811977</v>
       </c>
       <c r="E14" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F14" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>11.48909929957062</v>
+        <v>1.866978636180226</v>
       </c>
       <c r="D15" t="n">
-        <v>11.86710913406754</v>
+        <v>1.928405234285975</v>
       </c>
       <c r="E15" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F15" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.65851585427212</v>
+        <v>6.119508826319221</v>
       </c>
       <c r="D16" t="n">
-        <v>10.98738181142975</v>
+        <v>1.785449544357334</v>
       </c>
       <c r="E16" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F16" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>30.85699573943869</v>
+        <v>5.014261807658787</v>
       </c>
       <c r="D17" t="n">
-        <v>5.230621037072987</v>
+        <v>0.8499759185243604</v>
       </c>
       <c r="E17" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F17" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34.56719466193706</v>
+        <v>5.617169132564772</v>
       </c>
       <c r="D18" t="n">
-        <v>27.84510975331595</v>
+        <v>4.524830334913842</v>
       </c>
       <c r="E18" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F18" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>40.68325126588972</v>
+        <v>6.611028330707081</v>
       </c>
       <c r="D19" t="n">
-        <v>40.87528355554531</v>
+        <v>6.642233577776113</v>
       </c>
       <c r="E19" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F19" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>37.55212563133188</v>
+        <v>6.102220415091431</v>
       </c>
       <c r="D20" t="n">
-        <v>15.81890050338843</v>
+        <v>2.57057133180062</v>
       </c>
       <c r="E20" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F20" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>42.28068586969493</v>
+        <v>6.870611453825427</v>
       </c>
       <c r="D21" t="n">
-        <v>23.66956453596811</v>
+        <v>3.846304237094818</v>
       </c>
       <c r="E21" t="n">
-        <v>21.21630866183684</v>
+        <v>3.447650157548487</v>
       </c>
       <c r="F21" t="n">
-        <v>25.26570118572905</v>
+        <v>4.105676442680971</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
